--- a/Manual Testing/Bug report.xlsx
+++ b/Manual Testing/Bug report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f8e9f45186afbd9/Scans/placement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Madhumitha\IdeaProjects\TichiAutomation\Manual Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{556845D6-D055-475B-A4D8-2BF1895C935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A82CCAA-86AB-45E9-A31C-0E9DE5F9F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{13E26DB9-2AD3-4731-9242-619CF74AFA35}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{13E26DB9-2AD3-4731-9242-619CF74AFA35}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
   <si>
     <t>Bug ID</t>
   </si>
@@ -93,84 +93,6 @@
     <t>User must have a registered account and be on the Login page.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Open the Login page.2. Enter a valid registered email address.3. Enter an incorrect password.4. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The application should display a user-friendly error message such as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Invalid email or password."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and should not expose any internal server errors.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The application displays </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Internal server error"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> instead of an authentication error message.</t>
-    </r>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
@@ -204,53 +126,6 @@
     <t>Last Name field accepts excessively long input without validation</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Open the Signup page.2. Enter a very long value (100+ alphabetic characters) in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>First Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field.3. Fill the remaining mandatory fields.4. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>The application should restrict the input to the supported maximum length or display an appropriate validation message.</t>
   </si>
   <si>
@@ -260,53 +135,6 @@
     <t>BUG002_FirstName_Length.png</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Open the Signup page.2. Enter a very long value (100+ alphabetic characters) in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Last Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field.3. Fill the remaining mandatory fields.4. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>The application accepts a very long Last Name without any length validation and allows the user to proceed with registration.</t>
   </si>
   <si>
@@ -319,32 +147,6 @@
     <t>Email Address field accepts excessively long email input without validation</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Open the Signup page.2. Enter an email address exceeding the commonly supported maximum length (e.g., more than 254 characters).3. Fill the remaining mandatory fields.4. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>The application should restrict the email length or display an appropriate validation message.</t>
   </si>
   <si>
@@ -357,23 +159,31 @@
     <t>BUG_005</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Application allows login with an invalid email format </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Assumed Issue - Assignment)</t>
-    </r>
-  </si>
-  <si>
     <t>User is on the Login page.</t>
+  </si>
+  <si>
+    <t>The application should validate the email format, display an appropriate validation message, and prevent the login process.</t>
+  </si>
+  <si>
+    <t>1. Open the Login page.2. Enter a valid registered email address.3. Enter an incorrect password.4. Click Login.</t>
+  </si>
+  <si>
+    <t>The application should display a user-friendly error message such as "Invalid email or password." and should not expose any internal server errors.</t>
+  </si>
+  <si>
+    <t>The application displays "Internal server error" instead of an authentication error message.</t>
+  </si>
+  <si>
+    <t>1. Open the Signup page.2. Enter a very long value (100+ alphabetic characters) in the First Name field.3. Fill the remaining mandatory fields.4. Click Sign Up.</t>
+  </si>
+  <si>
+    <t>1. Open the Signup page.2. Enter a very long value (100+ alphabetic characters) in the Last Name field.3. Fill the remaining mandatory fields.4. Click Sign Up.</t>
+  </si>
+  <si>
+    <t>1. Open the Signup page.2. Enter an email address exceeding the commonly supported maximum length (e.g., more than 254 characters).3. Fill the remaining mandatory fields.4. Click Sign Up.</t>
+  </si>
+  <si>
+    <t>Assumed as per assignment: The application accepts the invalid email format and proceeds with the login process instead of displaying a validation error.</t>
   </si>
   <si>
     <r>
@@ -395,53 +205,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">).3. Enter any password.4. Click the </t>
+      <t>).3. Enter any password.4. Click the Login button.</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <t>The application should validate the email format, display an appropriate validation message, and prevent the login process.</t>
-  </si>
-  <si>
-    <r>
-      <t>Assumed as per assignment:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The application accepts the invalid email format and proceeds with the login process instead of displaying a validation error.</t>
-    </r>
-  </si>
-  <si>
-    <t>N/A (Assumed Issue as per Assignment)</t>
-  </si>
-  <si>
-    <t>alre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application allows login with an invalid email format </t>
+  </si>
+  <si>
+    <t>Invalidemail</t>
   </si>
 </sst>
 </file>
@@ -465,17 +236,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -486,7 +256,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -494,22 +264,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -826,19 +608,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8EFA37-D6BC-43D1-90D3-49276B349AE2}">
-  <dimension ref="A4:N13"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="20.21875" customWidth="1"/>
     <col min="2" max="2" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="24.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" customWidth="1"/>
+    <col min="7" max="7" width="34.88671875" customWidth="1"/>
+    <col min="8" max="8" width="47.44140625" customWidth="1"/>
+    <col min="9" max="9" width="41.5546875" customWidth="1"/>
     <col min="10" max="10" width="25.88671875" customWidth="1"/>
     <col min="12" max="12" width="14.109375" customWidth="1"/>
     <col min="13" max="13" width="16.21875" customWidth="1"/>
     <col min="14" max="14" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:14" ht="41.4" customHeight="1"/>
     <row r="4" spans="1:14" ht="28.8">
       <c r="A4" s="1" t="s">
         <v>0</v>
@@ -880,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="115.8" customHeight="1">
@@ -906,165 +691,165 @@
         <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="M5" s="3">
         <v>46205</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>25</v>
+      <c r="N5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="172.8">
       <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M6" s="3">
         <v>46206</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="172.8">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M7" s="3">
         <v>46206</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="199.2" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M8" s="3">
         <v>46206</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="144">
-      <c r="A9" s="4" t="s">
-        <v>46</v>
+    <row r="9" spans="1:14" ht="86.4">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>15</v>
@@ -1079,33 +864,28 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M9" s="3">
         <v>46206</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="B13" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
